--- a/results/[15_expiring_support_res]_#_fix_cost.xlsx
+++ b/results/[15_expiring_support_res]_#_fix_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2734.479376401644</v>
+        <v>7826.75228613598</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>33847.6339212341</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>6603.19413005156</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1773.994550154473</v>
+        <v>1803.232371121225</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1658.230358181116</v>
+        <v>2102.881687578508</v>
       </c>
       <c r="O2" t="n">
-        <v>1397.558403130994</v>
+        <v>1377.66219250799</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4893.736422177342</v>
+        <v>57176.22111707697</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>138539.6251440333</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>11516.76011754883</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5736.164476918771</v>
+        <v>5737.626367967108</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>5284.57682521633</v>
+        <v>9088.996366531621</v>
       </c>
       <c r="O2" t="n">
-        <v>4382.139292924096</v>
+        <v>4379.800966355691</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29138.97894437286</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>232873.1521521556</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>11659.35271551092</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9673.563003507486</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>10629.42549846868</v>
+        <v>19975.18324915363</v>
       </c>
       <c r="O2" t="n">
-        <v>7388.019004632071</v>
+        <v>7385.319102257901</v>
       </c>
     </row>
   </sheetData>
@@ -926,13 +926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29138.97894437286</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>232873.1521521556</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -941,13 +941,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>11659.35271551092</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9673.563003507486</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>11787.27525091185</v>
+        <v>21287.82254389593</v>
       </c>
       <c r="O2" t="n">
-        <v>7388.019004632071</v>
+        <v>7385.319102257901</v>
       </c>
     </row>
   </sheetData>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36809.53783853602</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>193.0947398408091</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>232873.1521521556</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>11659.35271551092</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9673.563003507486</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>14621.28053885259</v>
+        <v>21287.82254389593</v>
       </c>
       <c r="O2" t="n">
-        <v>8220.575700630221</v>
+        <v>8217.476074010643</v>
       </c>
     </row>
   </sheetData>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>36809.53783853602</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>193.0947398408091</v>
+        <v>20816.24951594921</v>
       </c>
       <c r="C2" t="n">
-        <v>232873.1521521556</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>11659.35271551092</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>9673.563003507486</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>14621.28053885259</v>
+        <v>21287.82254389593</v>
       </c>
       <c r="O2" t="n">
-        <v>8220.575700630221</v>
+        <v>8217.476074010643</v>
       </c>
     </row>
   </sheetData>

--- a/results/[15_expiring_support_res]_#_fix_cost.xlsx
+++ b/results/[15_expiring_support_res]_#_fix_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2276.6094180751</v>
+        <v>7826.75228613598</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>37868.01067536479</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>5785.128911090883</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1940.59546141152</v>
+        <v>1803.232371121225</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1276.743415676677</v>
+        <v>2102.881687578508</v>
       </c>
       <c r="O2" t="n">
-        <v>1265.771125157249</v>
+        <v>1377.66219250799</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13539.60804101515</v>
+        <v>57176.22111707697</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>222509.2947290669</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>13425.16262068724</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8333.250449478319</v>
+        <v>5737.626367967108</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>10719.45954832789</v>
+        <v>9088.996366531621</v>
       </c>
       <c r="O2" t="n">
-        <v>6864.3668299521</v>
+        <v>4379.800966355691</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13539.60804101515</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>222509.2947290669</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>13425.16262068724</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8333.250449478319</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>10719.45954832789</v>
+        <v>19975.18324915363</v>
       </c>
       <c r="O2" t="n">
-        <v>6864.3668299521</v>
+        <v>7385.319102257901</v>
       </c>
     </row>
   </sheetData>
@@ -926,13 +926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13539.60804101515</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>222509.2947290669</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -941,13 +941,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>13425.16262068724</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8333.250449478319</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>10719.45954832789</v>
+        <v>21287.82254389593</v>
       </c>
       <c r="O2" t="n">
-        <v>6864.3668299521</v>
+        <v>7385.319102257901</v>
       </c>
     </row>
   </sheetData>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13539.60804101515</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>4311.814902211931</v>
       </c>
       <c r="C2" t="n">
-        <v>222509.2947290669</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>13425.16262068724</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8333.250449478319</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>10719.45954832789</v>
+        <v>21287.82254389593</v>
       </c>
       <c r="O2" t="n">
-        <v>6864.3668299521</v>
+        <v>8217.476074010643</v>
       </c>
     </row>
   </sheetData>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13539.60804101515</v>
+        <v>105875.693651922</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>20816.24951594921</v>
       </c>
       <c r="C2" t="n">
-        <v>222509.2947290669</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>202806.8080011294</v>
       </c>
       <c r="F2" t="n">
-        <v>13425.16262068724</v>
+        <v>13254.31003192607</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8333.250449478319</v>
+        <v>9671.405456806198</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.547386017423</v>
       </c>
       <c r="N2" t="n">
-        <v>10719.45954832789</v>
+        <v>21287.82254389593</v>
       </c>
       <c r="O2" t="n">
-        <v>6864.3668299521</v>
+        <v>8217.476074010643</v>
       </c>
     </row>
   </sheetData>
